--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20232.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -79,64 +79,73 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ALMANZA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
   </si>
   <si>
     <t>ENRIQUEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>SOSA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
-  </si>
-  <si>
-    <t>SAMIR</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>BERMUDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>VANESA BETHSABE</t>
+  </si>
+  <si>
+    <t>AIDE SCARLET</t>
+  </si>
+  <si>
+    <t>KAREN</t>
+  </si>
+  <si>
+    <t>YAMILETH</t>
   </si>
   <si>
     <t>LUZ YESENIA</t>
   </si>
   <si>
-    <t>GISELA GUADALUPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>OSCAR ALEXANDER</t>
+    <t>SILVANA</t>
+  </si>
+  <si>
+    <t>GIANCARLO</t>
   </si>
 </sst>
 </file>
@@ -706,16 +715,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>36.67</v>
+      </c>
+      <c r="H2">
+        <v>5.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -729,16 +741,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>20.69</v>
+      </c>
+      <c r="H3">
+        <v>3.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -752,16 +767,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>54.55</v>
+      </c>
+      <c r="H4">
+        <v>5.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -775,16 +793,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>39.39</v>
+      </c>
+      <c r="H5">
+        <v>4.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -798,16 +819,19 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>41.67</v>
+      </c>
+      <c r="H6">
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>
@@ -863,16 +887,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>26.67</v>
+        <v>36.67</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -889,13 +913,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>24.14</v>
+        <v>20.69</v>
       </c>
       <c r="H3">
         <v>5.3</v>
@@ -915,16 +939,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>42.42</v>
+        <v>54.55</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -941,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>24.24</v>
+        <v>39.39</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -976,7 +1000,7 @@
         <v>41.67</v>
       </c>
       <c r="H6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -986,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1018,16 +1042,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920210</v>
+        <v>23330051920185</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1041,16 +1065,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920318</v>
+        <v>23330051920218</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1064,22 +1088,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920240</v>
+        <v>23330051920258</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1087,22 +1111,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920244</v>
+        <v>23330051920265</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1110,16 +1134,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920328</v>
+        <v>23330051920226</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1133,16 +1157,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920260</v>
+        <v>23330051920244</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1156,16 +1180,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920278</v>
+        <v>23330051920333</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1174,6 +1198,29 @@
         <v>12</v>
       </c>
       <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920300</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20232.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,75 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ALMANZA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>BERMUDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>VANESA BETHSABE</t>
-  </si>
-  <si>
-    <t>AIDE SCARLET</t>
-  </si>
-  <si>
-    <t>KAREN</t>
-  </si>
-  <si>
-    <t>YAMILETH</t>
-  </si>
-  <si>
-    <t>LUZ YESENIA</t>
-  </si>
-  <si>
-    <t>SILVANA</t>
-  </si>
-  <si>
-    <t>GIANCARLO</t>
   </si>
 </sst>
 </file>
@@ -887,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>36.67</v>
+        <v>76.67</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -913,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>20.69</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -939,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>54.55</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -965,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F5">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>39.39</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -991,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G6">
-        <v>41.67</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1040,190 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920185</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920218</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920258</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920265</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920226</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920244</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920333</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920300</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Villanueva Morales Luis Arturo - Estadisticos 20232.xlsx
+++ b/docentes/Villanueva Morales Luis Arturo - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>SERGIO EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -971,6 +980,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920208</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
